--- a/panele-sterowania/Panel-E.xlsx
+++ b/panele-sterowania/Panel-E.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gen-panel-e.py · 2026-06-29 09:36</t>
+          <t>gen-panel-e.py · 2026-07-09 18:14</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0…4 · opts: Malenki, Mały, Standardowy, Duży, Ogromny</t>
+          <t>0…5 · opts: Malenki, Mały, Standardowy, Duży, Ogromny, Super Huge</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Typy cywilizacji — indeks domyślny w opts</t>
+          <t>Liczba cywilizacji — indeks domyślny w opts</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
@@ -1608,17 +1608,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E-NG-forest_density</t>
+          <t>E-NG-map_quality</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>forest_density</t>
+          <t>map_quality</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Las (logiczny) — indeks domyślny w opts</t>
+          <t>Jakość grafiki mapy — indeks domyślny w opts</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
@@ -1626,20 +1626,100 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>0…2 · opts: Niska, Średnia, Wysoka</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>idx</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Domyślny wybór w kreatorze krok 4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>gra/data/ui-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>E-NG-forest_density</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>forest_density</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Las — indeks domyślny w opts</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>0…2 · opts: Mało, Normalnie, Dużo</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>idx</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Domyślny wybór w kreatorze krok 4</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>gra/data/ui-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>E-NG-relief_density</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>relief_density</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Góry i wzgórza — indeks domyślny w opts</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0…2 · opts: Mało, Normalnie, Dużo</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>idx</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Domyślny wybór w kreatorze krok 4</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>gra/data/ui-params.json</t>
         </is>
@@ -1729,7 +1809,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>0.1 • Kamień, Brąz &amp; Żelazo</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2004,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2196,7 +2276,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2236,7 +2316,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2396,7 +2476,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2436,7 +2516,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2596,7 +2676,7 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2636,7 +2716,7 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -2796,7 +2876,7 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2836,7 +2916,7 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2956,7 +3036,7 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2996,7 +3076,7 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>168</v>
+        <v>336</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -3036,7 +3116,7 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>119</v>
+        <v>238</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -3054,6 +3134,206 @@
         </is>
       </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>gra/data/e-start-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>E-MAP-Super Huge.rywale_ai</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Super Huge.rywale_ai</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Super Huge: Domyślna liczba rywali AI</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>liczba dodatnia</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>szt.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Gęstość starć na mapie</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>gra/data/e-start-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>E-MAP-Super Huge.miasta_panstwa</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Super Huge.miasta_panstwa</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Super Huge: Domyślna liczba miast w klastrze gracza</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>liczba dodatnia</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>szt.</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Suwak ±1 (Sparta, Kapua…)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>gra/data/e-start-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>E-MAP-Super Huge.typy_cywilizacji</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Super Huge.typy_cywilizacji</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Super Huge: Domyślna liczba obcych typów/klastrów</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>liczba dodatnia</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>szt.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Ta sama skala co miasta-państwa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>gra/data/e-start-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>E-MAP-Super Huge.hex_w</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Super Huge.hex_w</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Super Huge: Szerokość mapy w heksach</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>672</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>liczba dodatnia</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>hex</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Informacyjnie</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>gra/data/e-start-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>E-MAP-Super Huge.hex_h</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Super Huge.hex_h</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Super Huge: Wysokość mapy w heksach</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>476</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>liczba dodatnia</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>hex</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Informacyjnie</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>gra/data/e-start-params.json</t>
         </is>
@@ -3302,7 +3582,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3342,7 +3622,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3382,7 +3662,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3860,7 +4140,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3900,7 +4180,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3940,7 +4220,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>

--- a/panele-sterowania/Panel-E.xlsx
+++ b/panele-sterowania/Panel-E.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gen-panel-e.py · 2026-07-09 18:14</t>
+          <t>gen-panel-e.py · 2026-07-09 22:33</t>
         </is>
       </c>
     </row>

--- a/panele-sterowania/Panel-E.xlsx
+++ b/panele-sterowania/Panel-E.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gen-panel-e.py · 2026-07-09 22:33</t>
+          <t>gen-panel-e.py · 2026-07-19 21:54</t>
         </is>
       </c>
     </row>
